--- a/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9703_escuela-esperanza-joven_nt1_nucleos.xlsx
@@ -727,13 +727,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D647D363-E7FC-4C90-8627-D4E0A6827002}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F3C7849-DC75-4F94-B580-BC1507A8B8AF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3378E9F-EAB9-439E-97E5-8E5673BF580A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05DD18BD-D8D8-4E8E-8348-6212A2E16996}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6FBFF71-7FAD-4D56-AA93-3776E57F3A9B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2D16BAD-3997-4F32-BDB6-08247869E1E9}"/>
 </file>